--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8745,6 +8745,111 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127760144</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98471</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skrållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>385827</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6973404</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8750,7 +8750,7 @@
         <v>127760144</v>
       </c>
       <c r="B73" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72225318</v>
+        <v>104490869</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stig längs med Ljungan, Ljungdalen, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385828.1528213235</v>
+        <v>385670</v>
       </c>
       <c r="R2" t="n">
-        <v>6973212.842074684</v>
+        <v>6972989</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,70 +755,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Bergman</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Bergman</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104486086</v>
+        <v>104490900</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 3, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385878.4634345998</v>
+        <v>385711</v>
       </c>
       <c r="R3" t="n">
-        <v>6973343.995092962</v>
+        <v>6972966</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +844,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +854,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,37 +881,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104486614</v>
+        <v>104486147</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385774.7857901035</v>
+        <v>385818</v>
       </c>
       <c r="R4" t="n">
-        <v>6973177.708138492</v>
+        <v>6973145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,19 +950,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104490040</v>
+        <v>104486536</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,35 +990,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kläppvägen 10, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385586.7099842934</v>
+        <v>385782</v>
       </c>
       <c r="R5" t="n">
-        <v>6973096.581030332</v>
+        <v>6973145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,19 +1048,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,51 +1077,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104486462</v>
+        <v>104483254</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 12, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385780.2643502797</v>
+        <v>385814</v>
       </c>
       <c r="R6" t="n">
-        <v>6973124.991221779</v>
+        <v>6973378</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,19 +1146,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104486536</v>
+        <v>104482778</v>
       </c>
       <c r="B7" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,35 +1186,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385782.33526623</v>
+        <v>385864</v>
       </c>
       <c r="R7" t="n">
-        <v>6973145.015859553</v>
+        <v>6973343</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,19 +1244,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104486293</v>
+        <v>104482914</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,35 +1284,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385785.4009400345</v>
+        <v>385892</v>
       </c>
       <c r="R8" t="n">
-        <v>6973128.009227852</v>
+        <v>6973356</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,19 +1342,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,15 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104482358</v>
+        <v>104489411</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,35 +1382,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgen 12, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385781.6373006876</v>
+        <v>385614</v>
       </c>
       <c r="R9" t="n">
-        <v>6973347.829356259</v>
+        <v>6973145</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,19 +1440,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104484661</v>
+        <v>104484533</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385874.954678808</v>
+        <v>385843</v>
       </c>
       <c r="R10" t="n">
-        <v>6973308.949984766</v>
+        <v>6973340</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,19 +1538,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,15 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104491137</v>
+        <v>104486653</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,35 +1578,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älgen 4, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385719.1718673604</v>
+        <v>385783</v>
       </c>
       <c r="R11" t="n">
-        <v>6973078.251039916</v>
+        <v>6973185</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,19 +1636,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,51 +1665,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104490943</v>
+        <v>104482358</v>
       </c>
       <c r="B12" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älgen 3, Berg, Hjd</t>
+          <t>Älgen 12, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385714.4783049953</v>
+        <v>385781</v>
       </c>
       <c r="R12" t="n">
-        <v>6972956.91547809</v>
+        <v>6973348</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,19 +1734,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,15 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104486216</v>
+        <v>104485210</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,35 +1774,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Ljungdalen 279, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385797.0699983825</v>
+        <v>385946</v>
       </c>
       <c r="R13" t="n">
-        <v>6973160.944557144</v>
+        <v>6973209</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,19 +1832,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,12 +1864,7 @@
         <v>104486095</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385817.070280343</v>
+        <v>385818</v>
       </c>
       <c r="R14" t="n">
-        <v>6973144.260730976</v>
+        <v>6973145</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,19 +1930,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,15 +1959,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104489152</v>
+        <v>104486293</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,35 +1970,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385612.2725011725</v>
+        <v>385785</v>
       </c>
       <c r="R15" t="n">
-        <v>6973160.546211691</v>
+        <v>6973128</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2222,19 +2028,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,15 +2057,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104489397</v>
+        <v>104486875</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,14 +2089,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385614.4555041925</v>
+        <v>385775</v>
       </c>
       <c r="R16" t="n">
-        <v>6973144.483772759</v>
+        <v>6973249</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2335,19 +2126,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,15 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104488824</v>
+        <v>104488381</v>
       </c>
       <c r="B17" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385652.5053445619</v>
+        <v>385707</v>
       </c>
       <c r="R17" t="n">
-        <v>6973199.333845838</v>
+        <v>6973265</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2448,19 +2224,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,15 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104486875</v>
+        <v>104488659</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,14 +2285,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385775.0169926122</v>
+        <v>385661</v>
       </c>
       <c r="R18" t="n">
-        <v>6973249.864500963</v>
+        <v>6973252</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2563,7 +2324,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2334,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,27 +2349,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104486306</v>
+        <v>104488937</v>
       </c>
       <c r="B19" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,35 +2372,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385785.4009400345</v>
+        <v>385634</v>
       </c>
       <c r="R19" t="n">
-        <v>6973128.009227852</v>
+        <v>6973167</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,19 +2430,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,15 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104491213</v>
+        <v>104489397</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,14 +2491,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Älgen 4, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385688.887423393</v>
+        <v>385614</v>
       </c>
       <c r="R20" t="n">
-        <v>6973101.689489044</v>
+        <v>6973145</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2787,19 +2528,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,15 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104485951</v>
+        <v>104491042</v>
       </c>
       <c r="B21" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2842,35 +2568,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 3, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385828.4299772013</v>
+        <v>385742</v>
       </c>
       <c r="R21" t="n">
-        <v>6973194.56289848</v>
+        <v>6972984</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2900,19 +2626,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,51 +2655,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104486147</v>
+        <v>104491088</v>
       </c>
       <c r="B22" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>306</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 4, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385818.0157679995</v>
+        <v>385723</v>
       </c>
       <c r="R22" t="n">
-        <v>6973145.141240912</v>
+        <v>6973039</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3013,19 +2724,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,15 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104488744</v>
+        <v>104491213</v>
       </c>
       <c r="B23" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,35 +2764,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Älgen 4, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385674.5603094755</v>
+        <v>385688</v>
       </c>
       <c r="R23" t="n">
-        <v>6973202.217352532</v>
+        <v>6973102</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,19 +2822,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3165,15 +2851,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104486890</v>
+        <v>104483602</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,35 +2862,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 12, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385789.1925001259</v>
+        <v>385814</v>
       </c>
       <c r="R24" t="n">
-        <v>6973158.022204014</v>
+        <v>6973378</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,19 +2920,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,27 +2937,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104489528</v>
+        <v>104489693</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,35 +2960,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Kläppvägen 10, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385607.2792763614</v>
+        <v>385610</v>
       </c>
       <c r="R25" t="n">
-        <v>6973161.634203851</v>
+        <v>6973081</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3352,19 +3018,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,63 +3035,58 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104482914</v>
+        <v>104490943</v>
       </c>
       <c r="B26" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>2063</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 3, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385892.6128013662</v>
+        <v>385714</v>
       </c>
       <c r="R26" t="n">
-        <v>6973356.289835169</v>
+        <v>6972957</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3465,19 +3116,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,15 +3145,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104482778</v>
+        <v>104490040</v>
       </c>
       <c r="B27" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,35 +3156,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Kläppvägen 10, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385863.7821318086</v>
+        <v>385587</v>
       </c>
       <c r="R27" t="n">
-        <v>6973342.680158477</v>
+        <v>6973097</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3578,19 +3214,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,51 +3243,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104485210</v>
+        <v>104482779</v>
       </c>
       <c r="B28" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ljungdalen 279, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385946.4694325946</v>
+        <v>385864</v>
       </c>
       <c r="R28" t="n">
-        <v>6973208.717170603</v>
+        <v>6973343</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3691,19 +3312,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3730,51 +3341,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104485925</v>
+        <v>104484667</v>
       </c>
       <c r="B29" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385834.3686793515</v>
+        <v>385875</v>
       </c>
       <c r="R29" t="n">
-        <v>6973194.355755781</v>
+        <v>6973309</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,19 +3410,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,51 +3439,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104485978</v>
+        <v>104485093</v>
       </c>
       <c r="B30" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Ljungdalen 279, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385842.0937106303</v>
+        <v>385944</v>
       </c>
       <c r="R30" t="n">
-        <v>6973166.681873812</v>
+        <v>6973225</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3917,19 +3508,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,51 +3537,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104483346</v>
+        <v>104486213</v>
       </c>
       <c r="B31" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Älgen 12, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385814.2547318427</v>
+        <v>385797</v>
       </c>
       <c r="R31" t="n">
-        <v>6973378.204649099</v>
+        <v>6973161</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4030,19 +3606,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,15 +3635,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104484847</v>
+        <v>104488642</v>
       </c>
       <c r="B32" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,35 +3646,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385912.9117710284</v>
+        <v>385700</v>
       </c>
       <c r="R32" t="n">
-        <v>6973243.228219409</v>
+        <v>6973219</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4143,19 +3704,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,15 +3733,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104486653</v>
+        <v>104488785</v>
       </c>
       <c r="B33" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4198,35 +3744,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385783.7201722351</v>
+        <v>385664</v>
       </c>
       <c r="R33" t="n">
-        <v>6973184.704227397</v>
+        <v>6973200</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4256,19 +3802,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4295,51 +3831,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104486731</v>
+        <v>104489325</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Älgen 13, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385775.736121381</v>
+        <v>385614</v>
       </c>
       <c r="R34" t="n">
-        <v>6973191.833943347</v>
+        <v>6973145</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,19 +3900,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4408,15 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104490580</v>
+        <v>104489528</v>
       </c>
       <c r="B35" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4424,35 +3940,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kläppvägen 8, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385658.5877377452</v>
+        <v>385607</v>
       </c>
       <c r="R35" t="n">
-        <v>6972967.545929333</v>
+        <v>6973161</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4484,7 +4000,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4494,7 +4010,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4509,63 +4025,58 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104489411</v>
+        <v>104491137</v>
       </c>
       <c r="B36" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 4, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385614.4555041925</v>
+        <v>385719</v>
       </c>
       <c r="R36" t="n">
-        <v>6973144.483772759</v>
+        <v>6973078</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4595,19 +4106,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,15 +4135,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104489693</v>
+        <v>104482287</v>
       </c>
       <c r="B37" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4650,35 +4146,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppvägen 10, Berg, Hjd</t>
+          <t>Älgen 12, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385609.939420962</v>
+        <v>385767</v>
       </c>
       <c r="R37" t="n">
-        <v>6973080.696209057</v>
+        <v>6973345</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4708,19 +4204,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,15 +4233,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104488937</v>
+        <v>104482676</v>
       </c>
       <c r="B38" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4763,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4788,10 +4269,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385633.9984590017</v>
+        <v>385846</v>
       </c>
       <c r="R38" t="n">
-        <v>6973167.094962448</v>
+        <v>6973336</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4821,19 +4302,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4860,15 +4331,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104483602</v>
+        <v>104483346</v>
       </c>
       <c r="B39" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,21 +4342,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4901,10 +4367,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385814.2547318427</v>
+        <v>385814</v>
       </c>
       <c r="R39" t="n">
-        <v>6973378.204649099</v>
+        <v>6973378</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,19 +4400,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4973,15 +4429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104485093</v>
+        <v>104484661</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4989,35 +4440,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ljungdalen 279, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385944.284869098</v>
+        <v>385875</v>
       </c>
       <c r="R40" t="n">
-        <v>6973224.779004808</v>
+        <v>6973309</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5047,19 +4498,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,15 +4527,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104489424</v>
+        <v>104484908</v>
       </c>
       <c r="B41" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5102,35 +4538,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Ljungdalen 279, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385624.7180573231</v>
+        <v>385930</v>
       </c>
       <c r="R41" t="n">
-        <v>6973124.028173505</v>
+        <v>6973233</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5160,19 +4596,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,37 +4625,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104489100</v>
+        <v>104485804</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5240,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385625.9349713447</v>
+        <v>385860</v>
       </c>
       <c r="R42" t="n">
-        <v>6973171.944157754</v>
+        <v>6973196</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5273,19 +4694,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5312,15 +4723,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104491088</v>
+        <v>104485925</v>
       </c>
       <c r="B43" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5328,35 +4734,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Älgen 4, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385722.3864956281</v>
+        <v>385835</v>
       </c>
       <c r="R43" t="n">
-        <v>6973039.314295191</v>
+        <v>6973194</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5386,19 +4792,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5425,15 +4821,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104490462</v>
+        <v>104485978</v>
       </c>
       <c r="B44" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5462,14 +4853,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kläppvägen 8, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385640.4888526043</v>
+        <v>385842</v>
       </c>
       <c r="R44" t="n">
-        <v>6972973.2026641</v>
+        <v>6973166</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5499,19 +4890,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5538,15 +4919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104484667</v>
+        <v>104486306</v>
       </c>
       <c r="B45" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,35 +4930,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385874.954678808</v>
+        <v>385785</v>
       </c>
       <c r="R45" t="n">
-        <v>6973308.949984766</v>
+        <v>6973128</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5612,19 +4988,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,15 +5017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104484533</v>
+        <v>104488370</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5667,35 +5028,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385842.6260246574</v>
+        <v>385707</v>
       </c>
       <c r="R46" t="n">
-        <v>6973339.307521479</v>
+        <v>6973265</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5725,19 +5086,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5767,12 +5118,7 @@
         <v>104488510</v>
       </c>
       <c r="B47" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,10 +5151,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385682.7562113208</v>
+        <v>385683</v>
       </c>
       <c r="R47" t="n">
-        <v>6973253.54226117</v>
+        <v>6973253</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5838,19 +5184,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,15 +5213,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104488642</v>
+        <v>104488744</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5893,21 +5224,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5918,10 +5249,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385700.2908852779</v>
+        <v>385675</v>
       </c>
       <c r="R48" t="n">
-        <v>6973218.674786149</v>
+        <v>6973202</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5951,19 +5282,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5990,15 +5311,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104489325</v>
+        <v>104488824</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6006,35 +5322,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385614.4555041925</v>
+        <v>385653</v>
       </c>
       <c r="R49" t="n">
-        <v>6973144.483772759</v>
+        <v>6973199</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6064,19 +5380,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6103,15 +5409,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104490583</v>
+        <v>104490462</v>
       </c>
       <c r="B50" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6144,10 +5445,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385658.5877377452</v>
+        <v>385640</v>
       </c>
       <c r="R50" t="n">
-        <v>6972967.545929333</v>
+        <v>6972973</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6177,19 +5478,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,15 +5507,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104485804</v>
+        <v>104490583</v>
       </c>
       <c r="B51" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,14 +5539,14 @@
       <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Kläppvägen 8, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385860.4871459709</v>
+        <v>385658</v>
       </c>
       <c r="R51" t="n">
-        <v>6973195.728561484</v>
+        <v>6972967</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6290,19 +5576,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,51 +5605,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104490976</v>
+        <v>104489100</v>
       </c>
       <c r="B52" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Älgen 3, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385714.4783049953</v>
+        <v>385625</v>
       </c>
       <c r="R52" t="n">
-        <v>6972956.91547809</v>
+        <v>6973172</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6403,19 +5674,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6442,51 +5703,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104488381</v>
+        <v>104484847</v>
       </c>
       <c r="B53" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385707.8861772725</v>
+        <v>385913</v>
       </c>
       <c r="R53" t="n">
-        <v>6973265.909868848</v>
+        <v>6973244</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6516,19 +5772,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6555,51 +5801,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104488785</v>
+        <v>104490580</v>
       </c>
       <c r="B54" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Kläppvägen 8, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385663.5168975106</v>
+        <v>385658</v>
       </c>
       <c r="R54" t="n">
-        <v>6973200.319397839</v>
+        <v>6972967</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6629,19 +5870,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6668,15 +5899,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104482287</v>
+        <v>104482573</v>
       </c>
       <c r="B55" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6684,35 +5910,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Älgen 12, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385766.8922733082</v>
+        <v>385798</v>
       </c>
       <c r="R55" t="n">
-        <v>6973344.690203926</v>
+        <v>6973359</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6744,7 +5975,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6754,7 +5985,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6769,27 +6000,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104482676</v>
+        <v>104482699</v>
       </c>
       <c r="B56" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6797,35 +6023,40 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385845.6963662593</v>
+        <v>385846</v>
       </c>
       <c r="R56" t="n">
-        <v>6973335.546681707</v>
+        <v>6973336</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6855,19 +6086,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6894,15 +6115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104482779</v>
+        <v>104482790</v>
       </c>
       <c r="B57" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6910,35 +6126,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385863.7821318086</v>
+        <v>385864</v>
       </c>
       <c r="R57" t="n">
-        <v>6973342.680158477</v>
+        <v>6973343</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6968,19 +6189,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7007,15 +6218,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104488560</v>
+        <v>104483125</v>
       </c>
       <c r="B58" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7023,35 +6229,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385698.2776013738</v>
+        <v>385878</v>
       </c>
       <c r="R58" t="n">
-        <v>6973226.509612499</v>
+        <v>6973344</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7083,7 +6294,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7093,7 +6304,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7108,27 +6319,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104486213</v>
+        <v>104486015</v>
       </c>
       <c r="B59" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7136,35 +6342,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385797.0699983825</v>
+        <v>385842</v>
       </c>
       <c r="R59" t="n">
-        <v>6973160.944557144</v>
+        <v>6973166</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7194,19 +6405,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7233,15 +6434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104484908</v>
+        <v>104486349</v>
       </c>
       <c r="B60" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7249,35 +6445,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ljungdalen 279, Berg, Hjd</t>
+          <t>Älgen 13, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385929.9210355897</v>
+        <v>385803</v>
       </c>
       <c r="R60" t="n">
-        <v>6973232.58728893</v>
+        <v>6973105</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7307,19 +6508,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7346,15 +6537,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104483254</v>
+        <v>104488386</v>
       </c>
       <c r="B61" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7362,35 +6548,40 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Älgen 12, Berg, Hjd</t>
+          <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385814.2547318427</v>
+        <v>385710</v>
       </c>
       <c r="R61" t="n">
-        <v>6973378.204649099</v>
+        <v>6973259</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7422,7 +6613,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7432,7 +6623,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7447,27 +6638,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>104488370</v>
+        <v>104488502</v>
       </c>
       <c r="B62" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,35 +6661,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Älgen 6, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385707.8861772725</v>
+        <v>385701</v>
       </c>
       <c r="R62" t="n">
-        <v>6973265.909868848</v>
+        <v>6973305</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7535,7 +6726,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7545,7 +6736,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7560,27 +6751,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104491313</v>
+        <v>104488765</v>
       </c>
       <c r="B63" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7588,35 +6774,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Älgen 5, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385720.7580199826</v>
+        <v>385664</v>
       </c>
       <c r="R63" t="n">
-        <v>6973189.185575842</v>
+        <v>6973200</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7646,19 +6837,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7685,15 +6866,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>104482790</v>
+        <v>104490665</v>
       </c>
       <c r="B64" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7727,14 +6903,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Kläppvägen 8, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385863.7821318086</v>
+        <v>385633</v>
       </c>
       <c r="R64" t="n">
-        <v>6973342.680158477</v>
+        <v>6972938</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7766,7 +6942,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7776,7 +6952,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7791,27 +6967,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>104482573</v>
+        <v>104491116</v>
       </c>
       <c r="B65" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7840,19 +7011,19 @@
       <c r="K65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Älgen 12, Berg, Hjd</t>
+          <t>Älgen 3, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385797.5664837714</v>
+        <v>385718</v>
       </c>
       <c r="R65" t="n">
-        <v>6973358.691441686</v>
+        <v>6972958</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7884,7 +7055,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7894,7 +7065,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7921,32 +7092,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>104488765</v>
+        <v>104485293</v>
       </c>
       <c r="B66" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7958,19 +7124,19 @@
       <c r="K66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Ljungdalen 279, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385663.5168975106</v>
+        <v>385961</v>
       </c>
       <c r="R66" t="n">
-        <v>6973200.319397839</v>
+        <v>6973205</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8000,19 +7166,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8039,59 +7195,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>104482699</v>
+        <v>127760144</v>
       </c>
       <c r="B67" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Skrållan, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385845.6963662593</v>
+        <v>385827</v>
       </c>
       <c r="R67" t="n">
-        <v>6973335.546681707</v>
+        <v>6973404</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8115,22 +7264,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8145,71 +7284,68 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Bergström, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>104490665</v>
+        <v>72225318</v>
       </c>
       <c r="B68" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kläppvägen 8, Berg, Hjd</t>
+          <t>Stig längs med Ljungan, Ljungdalen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385632.8496468316</v>
+        <v>385828</v>
       </c>
       <c r="R68" t="n">
-        <v>6972937.841158506</v>
+        <v>6973213</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8233,22 +7369,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8257,74 +7393,65 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Thomas Bergman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Thomas Bergman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104488386</v>
+        <v>104488273</v>
       </c>
       <c r="B69" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Älgen 5, Berg, Hjd</t>
+          <t>Älgen 6, Berg, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385710.8767991299</v>
+        <v>385710</v>
       </c>
       <c r="R69" t="n">
-        <v>6973259.867940788</v>
+        <v>6973330</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8354,19 +7481,9 @@
           <t>2022-11-05</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8381,474 +7498,15 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>104486015</v>
-      </c>
-      <c r="B70" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Älgen 13, Berg, Hjd</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>385842.0937106303</v>
-      </c>
-      <c r="R70" t="n">
-        <v>6973166.681873812</v>
-      </c>
-      <c r="S70" t="n">
-        <v>25</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>104486349</v>
-      </c>
-      <c r="B71" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Älgen 13, Berg, Hjd</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>385803.7762218454</v>
-      </c>
-      <c r="R71" t="n">
-        <v>6973104.073845735</v>
-      </c>
-      <c r="S71" t="n">
-        <v>25</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>104483125</v>
-      </c>
-      <c r="B72" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Berg, Hjd</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>385878.4634345998</v>
-      </c>
-      <c r="R72" t="n">
-        <v>6973343.995092962</v>
-      </c>
-      <c r="S72" t="n">
-        <v>25</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>127760144</v>
-      </c>
-      <c r="B73" t="n">
-        <v>98592</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Skrållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>385827</v>
-      </c>
-      <c r="R73" t="n">
-        <v>6973404</v>
-      </c>
-      <c r="S73" t="n">
-        <v>50</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486147</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486536</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104483254</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489411</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484533</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486653</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482358</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486095</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486293</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486875</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2250,6 +2330,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488381</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488659</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488937</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489397</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104491042</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2750,6 +2855,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104491088</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,6 +2958,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104491213</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2946,6 +3061,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104483602</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3044,6 +3164,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489693</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3142,6 +3267,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490943</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,6 +3370,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490040</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3338,6 +3473,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482779</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3436,6 +3576,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484667</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3534,6 +3679,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485093</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3632,6 +3782,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486213</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3730,6 +3885,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488642</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3828,6 +3988,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488785</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3926,6 +4091,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489325</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4034,6 +4204,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489528</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4132,6 +4307,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104491137</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4230,6 +4410,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482287</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4328,6 +4513,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482676</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4426,6 +4616,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104483346</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4524,6 +4719,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484661</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4622,6 +4822,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484908</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4720,6 +4925,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485804</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4818,6 +5028,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485925</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4916,6 +5131,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485978</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5014,6 +5234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486306</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5112,6 +5337,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488370</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5210,6 +5440,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488510</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5308,6 +5543,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488744</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5406,6 +5646,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488824</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5504,6 +5749,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490462</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5602,6 +5852,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490583</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5700,6 +5955,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104489100</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5798,6 +6058,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104484847</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5896,6 +6161,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490580</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6009,6 +6279,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482573</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6112,6 +6387,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482699</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6215,6 +6495,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104482790</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6328,6 +6613,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104483125</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6431,6 +6721,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486015</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6534,6 +6829,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104486349</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6647,6 +6947,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488386</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6760,6 +7065,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488502</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6863,6 +7173,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488765</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6976,6 +7291,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104490665</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7089,6 +7409,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104491116</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7192,6 +7517,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104485293</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7297,6 +7627,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127760144</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7409,6 +7744,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72225318</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7507,8 +7847,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104488273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>